--- a/ValueSet-risk-factor-vs.xlsx
+++ b/ValueSet-risk-factor-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-risk-factor-vs.xlsx
+++ b/ValueSet-risk-factor-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-risk-factor-vs.xlsx
+++ b/ValueSet-risk-factor-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-risk-factor-vs.xlsx
+++ b/ValueSet-risk-factor-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-risk-factor-vs.xlsx
+++ b/ValueSet-risk-factor-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-risk-factor-vs.xlsx
+++ b/ValueSet-risk-factor-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -218,6 +218,12 @@
   </si>
   <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>smoking-last-10-years</t>
+  </si>
+  <si>
+    <t>Smoking within the last 10 years</t>
   </si>
   <si>
     <t>http://qualityregistry.org/CodeSystem/risk-factor-cs</t>
@@ -658,7 +664,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -683,18 +689,26 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>68</v>
+      <c r="B5" t="s" s="2">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
